--- a/output/介護保険事業計画_前期計画の評価_実施要領.xlsx
+++ b/output/介護保険事業計画_前期計画の評価_実施要領.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_自治体確認事項" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_落とし穴と対処" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_工程と成果物" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_計画期間中の推計の見直し" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1179,6 +1180,189 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>計画期間中の推計の見直しの手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="56" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>前期計画の評価は、計画期間中に推計を見直す手順があったかどうかに左右されます。見直す手順がないまま推計が実績と乖離し続けると、次期の計画で乖離の理由を説明できなくなります。次期の計画に置く年次評価の手順として示します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>【年次評価において推計の妥当性を確認する】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>確認する事項</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>確認の方法</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>見直しの基準</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>見直しを行う時期</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>年齢階級別の認定率</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>65〜74歳・75〜84歳・85歳以上の認定率の実績を各年度3月末で算定し、計画の前提と対比する</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>いずれかの階級で計画の前提から2年続けて乖離した場合</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>中間年（3年計画の2年度目）</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="10" t="n"/>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>認定者数</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>実績と計画の見込みを対比する</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>乖離が2年続けて2％を超えた場合</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>中間年</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>人口</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>住民基本台帳の実績と推計上の年齢階級別人口を対比する</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>総合戦略の改定又は国勢調査に基づく新しい推計の公表があった場合</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>差替えの要否を計画作成委員会に諮る</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>給付費</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>必要保険料月額と条例基準額の差を年度ごとに確認する</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>基金残高の見込みと併せて、次期の保険料設定の材料とする</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>毎年度</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="92" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>注1）見直しを行う場合も、推計の基礎（総合戦略上の人口及び住民基本台帳の実績趨勢）は変更しない。見直すのは認定率の前提である。
+注2）大雪地区広域連合の第9期においては、需要推計が実績を令和6年度2.9％、令和7年度3.5％上回ったが、期中に推計を見直す手順がなかった。第10期計画では本手順を年次評価に置く。
+注3）本手順は計画素案 第1章第6節から移したものである（令和8年9月29日のご指示による）。計画素案の本文には、4つを計画の前提と対比し乖離が2年続いた場合は中間年に推計を見直すこと、見直すのは認定率の前提であることを1段落で残している。
+注4）検証の結果を踏まえた見直しを行うこと及び結果を公表することは、保険者機能強化推進交付金等の評価指標が求める事項でもある。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
